--- a/cuadros/MAYO/BARQUISIMETO.xlsx
+++ b/cuadros/MAYO/BARQUISIMETO.xlsx
@@ -25,12 +25,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FFC6EFCE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -45,8 +51,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -412,197 +419,139 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>SUCURSAL</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>PROVEEDOR</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>FACTURA</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>FECHA</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>TIPO FISCALIZACIÓN</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>RESPONSABLE</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>INCIDENCIA</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>TIPO DE ERROR</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>OBSERVACIÓN</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>MONTO $</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>F COBRADA</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>CLASIFICACIÓN MONTO</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>SUCURSAL</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>PROVEEDOR</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>FACTURA</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>FECHA</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>TIPO DE FISCALIZACION</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>RESPONSABLE</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>INCIDENCIA</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>TIPO DE ERROR</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>OBSERVACIONES</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>F COBRADA</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HIST_20260501_0</t>
+          <t>BARQUISIMETO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BARQUISIMETO</t>
+          <t>VICAR</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ALIMENTOS MUNCHY, C.A.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>4734</v>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>RECEPCION</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>RECEPCION</t>
+          <t>AGEL</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>REIDINSON MONTERO</t>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>PRODUCTO O SKU DUPLICADO.</t>
+          <t>TIPO D</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>TIPO B</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>SKU DUPLICADO</t>
+          <t>COBOR 20</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="n">
+        <v>211.98</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1123</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>NINGUNA</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>HIST_20260501_1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>BARQUISIMETO</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>CAVA LUXOR</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>4934</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>RECEPCION</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>REIDINSON MONTERO</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>PRODUCTO O SKU DUPLICADO.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>TIPO B</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>SKU DUPLICADO</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>NINGUNA</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
+          <t>COBRO</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>20260503231844</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/BARQUISIMETO.xlsx
+++ b/cuadros/MAYO/BARQUISIMETO.xlsx
@@ -1,42 +1,136 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
+  <si>
+    <t>SUCURSAL</t>
+  </si>
+  <si>
+    <t>PROVEEDOR</t>
+  </si>
+  <si>
+    <t>FACTURA</t>
+  </si>
+  <si>
+    <t>FECHA</t>
+  </si>
+  <si>
+    <t>TIPO FISCALIZACIÓN</t>
+  </si>
+  <si>
+    <t>RESPONSABLE</t>
+  </si>
+  <si>
+    <t>INCIDENCIA</t>
+  </si>
+  <si>
+    <t>TIPO DE ERROR</t>
+  </si>
+  <si>
+    <t>OBSERVACIÓN</t>
+  </si>
+  <si>
+    <t>MONTO $</t>
+  </si>
+  <si>
+    <t>F COBRADA</t>
+  </si>
+  <si>
+    <t>CLASIFICACIÓN MONTO</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>BARQUISIMETO</t>
+  </si>
+  <si>
+    <t>ALIMENTOS MUNCHY, C.A.</t>
+  </si>
+  <si>
+    <t>RUBROS SANARE C2, C.A.</t>
+  </si>
+  <si>
+    <t>31976</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>RECEPCION</t>
+  </si>
+  <si>
+    <t>DEVOLUCION</t>
+  </si>
+  <si>
+    <t>REIDINSON MONTERO</t>
+  </si>
+  <si>
+    <t>PRODUCTO O SKU DUPLICADO.</t>
+  </si>
+  <si>
+    <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+  </si>
+  <si>
+    <t>TIPO B</t>
+  </si>
+  <si>
+    <t>TIPO A</t>
+  </si>
+  <si>
+    <t>SKU DUPLICADO</t>
+  </si>
+  <si>
+    <t>NRO DE DOCUMENTO ERRADO</t>
+  </si>
+  <si>
+    <t>SIN FOTO</t>
+  </si>
+  <si>
+    <t>NINGUNA</t>
+  </si>
+  <si>
+    <t>20260504092500</t>
+  </si>
+  <si>
+    <t>20260504112100</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor rgb="FFC6EFCE"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -51,82 +145,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -414,144 +440,131 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>SUCURSAL</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>PROVEEDOR</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>FACTURA</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>FECHA</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>TIPO FISCALIZACIÓN</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>RESPONSABLE</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>INCIDENCIA</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>TIPO DE ERROR</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>OBSERVACIÓN</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>MONTO $</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>F COBRADA</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>CLASIFICACIÓN MONTO</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
+    <row r="1" spans="1:13">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>BARQUISIMETO</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>VICAR</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>RECEPCION</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>AGEL</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>TIPO D</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>COBOR 20</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="n">
-        <v>211.98</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>1123</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>COBRO</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>20260503231844</t>
-        </is>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2">
+        <v>4734</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/BARQUISIMETO.xlsx
+++ b/cuadros/MAYO/BARQUISIMETO.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="36">
   <si>
     <t>SUCURSAL</t>
   </si>
@@ -64,7 +64,10 @@
     <t>RUBROS SANARE C2, C.A.</t>
   </si>
   <si>
-    <t>31976</t>
+    <t>ALIMENTOS BOTALON, C.A.</t>
+  </si>
+  <si>
+    <t>A3-023938</t>
   </si>
   <si>
     <t>2026-05-01</t>
@@ -82,6 +85,9 @@
     <t>REIDINSON MONTERO</t>
   </si>
   <si>
+    <t>RUBER RAMOS</t>
+  </si>
+  <si>
     <t>PRODUCTO O SKU DUPLICADO.</t>
   </si>
   <si>
@@ -100,6 +106,9 @@
     <t>NRO DE DOCUMENTO ERRADO</t>
   </si>
   <si>
+    <t>NRO DE FACRURA ERRADO</t>
+  </si>
+  <si>
     <t>SIN FOTO</t>
   </si>
   <si>
@@ -110,6 +119,9 @@
   </si>
   <si>
     <t>20260504112100</t>
+  </si>
+  <si>
+    <t>20260504125319</t>
   </si>
 </sst>
 </file>
@@ -441,7 +453,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -496,34 +508,34 @@
         <v>4734</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="M2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -533,38 +545,79 @@
       <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
-        <v>16</v>
+      <c r="C3">
+        <v>31976</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="M3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" t="s">
         <v>31</v>
+      </c>
+      <c r="L4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/BARQUISIMETO.xlsx
+++ b/cuadros/MAYO/BARQUISIMETO.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="40">
   <si>
     <t>SUCURSAL</t>
   </si>
@@ -67,9 +67,15 @@
     <t>ALIMENTOS BOTALON, C.A.</t>
   </si>
   <si>
+    <t>INDISTRIAS MAROS, C.A.</t>
+  </si>
+  <si>
     <t>A3-023938</t>
   </si>
   <si>
+    <t>C050346</t>
+  </si>
+  <si>
     <t>2026-05-01</t>
   </si>
   <si>
@@ -109,6 +115,9 @@
     <t>NRO DE FACRURA ERRADO</t>
   </si>
   <si>
+    <t>NRO DE CONTROL ARREDO</t>
+  </si>
+  <si>
     <t>SIN FOTO</t>
   </si>
   <si>
@@ -122,6 +131,9 @@
   </si>
   <si>
     <t>20260504125319</t>
+  </si>
+  <si>
+    <t>20260504145211</t>
   </si>
 </sst>
 </file>
@@ -453,7 +465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -508,34 +520,34 @@
         <v>4734</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="M2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -549,34 +561,34 @@
         <v>31976</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="M3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -587,37 +599,78 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="M4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" t="s">
         <v>35</v>
+      </c>
+      <c r="M5" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/BARQUISIMETO.xlsx
+++ b/cuadros/MAYO/BARQUISIMETO.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="46">
   <si>
     <t>SUCURSAL</t>
   </si>
@@ -55,6 +55,9 @@
     <t>ID</t>
   </si>
   <si>
+    <t>FOTO_INCIDENCIA</t>
+  </si>
+  <si>
     <t>BARQUISIMETO</t>
   </si>
   <si>
@@ -67,12 +70,18 @@
     <t>ALIMENTOS BOTALON, C.A.</t>
   </si>
   <si>
+    <t>COCA-COLA FEMSA DE VENEZUELA, S.A.</t>
+  </si>
+  <si>
     <t>INDISTRIAS MAROS, C.A.</t>
   </si>
   <si>
     <t>A3-023938</t>
   </si>
   <si>
+    <t>20FP7396069</t>
+  </si>
+  <si>
     <t>C050346</t>
   </si>
   <si>
@@ -82,6 +91,9 @@
     <t>2026-05-04</t>
   </si>
   <si>
+    <t>2026-05-05</t>
+  </si>
+  <si>
     <t>RECEPCION</t>
   </si>
   <si>
@@ -100,12 +112,18 @@
     <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
   </si>
   <si>
+    <t>PRODUCTO O SKU NO PERTENECE A LA RECEPCIÓN.</t>
+  </si>
+  <si>
     <t>TIPO B</t>
   </si>
   <si>
     <t>TIPO A</t>
   </si>
   <si>
+    <t>TIPO C</t>
+  </si>
+  <si>
     <t>SKU DUPLICADO</t>
   </si>
   <si>
@@ -115,22 +133,22 @@
     <t>NRO DE FACRURA ERRADO</t>
   </si>
   <si>
-    <t>NRO DE CONTROL ARREDO</t>
+    <t xml:space="preserve">SE AGREGO EL SKU DE FRESCOLITA 2 LT Y ERA FRESCOLITA 1.5 LT </t>
+  </si>
+  <si>
+    <t>NRO DE CONTROL ERRADO</t>
   </si>
   <si>
     <t>SIN FOTO</t>
   </si>
   <si>
+    <t>SIN_FOTO</t>
+  </si>
+  <si>
     <t>NINGUNA</t>
   </si>
   <si>
-    <t>20260504092500</t>
-  </si>
-  <si>
-    <t>20260504112100</t>
-  </si>
-  <si>
-    <t>20260504125319</t>
+    <t>ID_20260505105654</t>
   </si>
   <si>
     <t>20260504145211</t>
@@ -465,10 +483,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -508,169 +526,213 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2">
         <v>4734</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="I2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="L2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M2" t="s">
-        <v>36</v>
+        <v>43</v>
+      </c>
+      <c r="M2">
+        <v>20260504092500</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3">
         <v>31976</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H3" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I3" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L3" t="s">
+        <v>43</v>
+      </c>
+      <c r="M3">
+        <v>20260504112100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" t="s">
         <v>34</v>
       </c>
-      <c r="L3" t="s">
-        <v>35</v>
-      </c>
-      <c r="M3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" t="s">
-        <v>29</v>
-      </c>
       <c r="I4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="L4" t="s">
+        <v>43</v>
+      </c>
+      <c r="M4">
+        <v>20260504125319</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" t="s">
         <v>35</v>
       </c>
-      <c r="M4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" t="s">
-        <v>29</v>
-      </c>
       <c r="I5" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5" t="s">
+        <v>42</v>
+      </c>
+      <c r="L5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" t="s">
         <v>34</v>
       </c>
-      <c r="L5" t="s">
-        <v>35</v>
-      </c>
-      <c r="M5" t="s">
-        <v>39</v>
+      <c r="I6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" t="s">
+        <v>41</v>
+      </c>
+      <c r="L6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M6" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/BARQUISIMETO.xlsx
+++ b/cuadros/MAYO/BARQUISIMETO.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -997,6 +997,72 @@
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BARQUISIMETO</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>INVERSIONES LA PATRONAS 2024, C.A.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>000667</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>RUBER RAMOS</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ERROR DE KG EN TARA.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ERROR AL COLOCAR EL NRO DE CESTAS EN LA TARA , LO QUE ORIGINO UNA DIFERENCIA 2.5 KL DE GUAYABA </t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>RECUPERACIÓN</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ID_20260507074036</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/BARQUISIMETO.xlsx
+++ b/cuadros/MAYO/BARQUISIMETO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,6 +1063,72 @@
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BARQUISIMETO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ISOLA FOODS, C.A.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>7822</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>RUBER RAMOS</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU DUPLICADO.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SE DUPLICO EL SKU DEL MAIZ DULCE 250 GR OLE </t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ID_20260508093001</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/BARQUISIMETO.xlsx
+++ b/cuadros/MAYO/BARQUISIMETO.xlsx
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -548,7 +555,6 @@
       <c r="M2" t="n">
         <v>20260504092500</v>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -610,7 +616,6 @@
       <c r="M3" t="n">
         <v>20260504112100</v>
       </c>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -674,7 +679,6 @@
       <c r="M4" t="n">
         <v>20260504125319</v>
       </c>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -740,7 +744,6 @@
           <t>ID_20260505105654</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -806,7 +809,6 @@
           <t>20260504145211</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -872,7 +874,6 @@
           <t>ID_20260505153706</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -885,7 +886,6 @@
           <t>CAVA LUXOR</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>2026-05-05</t>
@@ -896,7 +896,6 @@
           <t>RECEPCION</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
@@ -930,7 +929,6 @@
           <t>ID_20260506083010</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -996,7 +994,6 @@
           <t>ID_20260506112808</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1044,7 +1041,7 @@
           <t xml:space="preserve">ERROR AL COLOCAR EL NRO DE CESTAS EN LA TARA , LO QUE ORIGINO UNA DIFERENCIA 2.5 KL DE GUAYABA </t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="1" t="n">
         <v>2.12</v>
       </c>
       <c r="K10" t="inlineStr">
@@ -1062,7 +1059,6 @@
           <t>ID_20260507074036</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1128,7 +1124,6 @@
           <t>ID_20260508093001</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/BARQUISIMETO.xlsx
+++ b/cuadros/MAYO/BARQUISIMETO.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor rgb="FFFFC000"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,6 +548,7 @@
       <c r="M2" t="n">
         <v>20260504092500</v>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -616,6 +610,7 @@
       <c r="M3" t="n">
         <v>20260504112100</v>
       </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -679,6 +674,7 @@
       <c r="M4" t="n">
         <v>20260504125319</v>
       </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -744,6 +740,7 @@
           <t>ID_20260505105654</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -809,6 +806,7 @@
           <t>20260504145211</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -874,6 +872,7 @@
           <t>ID_20260505153706</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -886,6 +885,7 @@
           <t>CAVA LUXOR</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>2026-05-05</t>
@@ -896,6 +896,7 @@
           <t>RECEPCION</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
@@ -929,6 +930,7 @@
           <t>ID_20260506083010</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -994,6 +996,7 @@
           <t>ID_20260506112808</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1041,7 +1044,7 @@
           <t xml:space="preserve">ERROR AL COLOCAR EL NRO DE CESTAS EN LA TARA , LO QUE ORIGINO UNA DIFERENCIA 2.5 KL DE GUAYABA </t>
         </is>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" t="n">
         <v>2.12</v>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,6 +1062,7 @@
           <t>ID_20260507074036</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1124,6 +1128,73 @@
           <t>ID_20260508093001</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BARQUISIMETO</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ALMEN GROUPP, C.A.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>REIDINSON MONTERO</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>NRO DE FACTURA ERRADO</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ID_20260512135450</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/BARQUISIMETO.xlsx
+++ b/cuadros/MAYO/BARQUISIMETO.xlsx
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -548,7 +555,6 @@
       <c r="M2" t="n">
         <v>20260504092500</v>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -610,7 +616,6 @@
       <c r="M3" t="n">
         <v>20260504112100</v>
       </c>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -674,7 +679,6 @@
       <c r="M4" t="n">
         <v>20260504125319</v>
       </c>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -740,7 +744,6 @@
           <t>ID_20260505105654</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -806,7 +809,6 @@
           <t>20260504145211</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -872,7 +874,6 @@
           <t>ID_20260505153706</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -885,7 +886,6 @@
           <t>CAVA LUXOR</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>2026-05-05</t>
@@ -896,7 +896,6 @@
           <t>RECEPCION</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
@@ -930,7 +929,6 @@
           <t>ID_20260506083010</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -996,7 +994,6 @@
           <t>ID_20260506112808</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1044,7 +1041,7 @@
           <t xml:space="preserve">ERROR AL COLOCAR EL NRO DE CESTAS EN LA TARA , LO QUE ORIGINO UNA DIFERENCIA 2.5 KL DE GUAYABA </t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="1" t="n">
         <v>2.12</v>
       </c>
       <c r="K10" t="inlineStr">
@@ -1062,7 +1059,6 @@
           <t>ID_20260507074036</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1128,7 +1124,6 @@
           <t>ID_20260508093001</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1194,7 +1189,6 @@
           <t>ID_20260512135450</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/BARQUISIMETO.xlsx
+++ b/cuadros/MAYO/BARQUISIMETO.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor rgb="FFFFC000"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,6 +548,7 @@
       <c r="M2" t="n">
         <v>20260504092500</v>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -616,6 +610,7 @@
       <c r="M3" t="n">
         <v>20260504112100</v>
       </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -679,6 +674,7 @@
       <c r="M4" t="n">
         <v>20260504125319</v>
       </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -744,6 +740,7 @@
           <t>ID_20260505105654</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -809,6 +806,7 @@
           <t>20260504145211</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -874,6 +872,7 @@
           <t>ID_20260505153706</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -886,6 +885,7 @@
           <t>CAVA LUXOR</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>2026-05-05</t>
@@ -896,6 +896,7 @@
           <t>RECEPCION</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
@@ -929,6 +930,7 @@
           <t>ID_20260506083010</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -994,6 +996,7 @@
           <t>ID_20260506112808</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1041,7 +1044,7 @@
           <t xml:space="preserve">ERROR AL COLOCAR EL NRO DE CESTAS EN LA TARA , LO QUE ORIGINO UNA DIFERENCIA 2.5 KL DE GUAYABA </t>
         </is>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" t="n">
         <v>2.12</v>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,6 +1062,7 @@
           <t>ID_20260507074036</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1124,6 +1128,7 @@
           <t>ID_20260508093001</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1189,6 +1194,73 @@
           <t>ID_20260512135450</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BARQUISIMETO</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C.A. SUCESORADEJOSEPUIG &amp; CIA </t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1856680</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>REIDINSON MONTERO</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>DOCUMENTACIÓN ERRÓNEA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SE CARGO LA FACTURA ERRADA </t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ID_20260513144726</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/BARQUISIMETO.xlsx
+++ b/cuadros/MAYO/BARQUISIMETO.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="88">
   <si>
     <t>SUCURSAL</t>
   </si>
@@ -97,6 +97,9 @@
     <t xml:space="preserve">C.A. SUCESORA DE JOSE PUIG &amp; CIA </t>
   </si>
   <si>
+    <t>PEPSI-COLA DE VENEZUELA, C.A.</t>
+  </si>
+  <si>
     <t>A3-023938</t>
   </si>
   <si>
@@ -127,6 +130,9 @@
     <t>1856679</t>
   </si>
   <si>
+    <t>7774367127</t>
+  </si>
+  <si>
     <t>2026-05-01</t>
   </si>
   <si>
@@ -226,6 +232,9 @@
     <t xml:space="preserve">SE CARGO LA FACTURA ERRONEA </t>
   </si>
   <si>
+    <t xml:space="preserve">SE DUPLICO EL SKU DE PEPSI DE 2 LTS </t>
+  </si>
+  <si>
     <t>SIN FOTO</t>
   </si>
   <si>
@@ -266,6 +275,9 @@
   </si>
   <si>
     <t>ID_20260513165342</t>
+  </si>
+  <si>
+    <t>ID_20260513170211</t>
   </si>
 </sst>
 </file>
@@ -597,7 +609,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -655,31 +667,31 @@
         <v>4734</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M2">
         <v>20260504092500</v>
@@ -696,31 +708,31 @@
         <v>31976</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M3">
         <v>20260504112100</v>
@@ -734,34 +746,34 @@
         <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M4">
         <v>20260504125319</v>
@@ -775,37 +787,37 @@
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="L5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -816,37 +828,37 @@
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -857,37 +869,37 @@
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="L7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M7" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -898,31 +910,31 @@
         <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="L8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -933,37 +945,37 @@
         <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="L9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M9" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -974,37 +986,37 @@
         <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J10">
         <v>2.12</v>
       </c>
       <c r="K10" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="L10" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="M10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1015,37 +1027,37 @@
         <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="L11" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M11" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1056,37 +1068,37 @@
         <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I12" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="L12" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1097,37 +1109,37 @@
         <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F13" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H13" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="L13" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M13" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1138,37 +1150,78 @@
         <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F14" t="s">
+        <v>48</v>
+      </c>
+      <c r="G14" t="s">
+        <v>55</v>
+      </c>
+      <c r="H14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I14" t="s">
+        <v>71</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" t="s">
+        <v>74</v>
+      </c>
+      <c r="L14" t="s">
+        <v>75</v>
+      </c>
+      <c r="M14" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" t="s">
         <v>46</v>
       </c>
-      <c r="G14" t="s">
-        <v>53</v>
-      </c>
-      <c r="H14" t="s">
-        <v>54</v>
-      </c>
-      <c r="I14" t="s">
-        <v>69</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14" t="s">
-        <v>71</v>
-      </c>
-      <c r="L14" t="s">
+      <c r="F15" t="s">
+        <v>49</v>
+      </c>
+      <c r="G15" t="s">
+        <v>50</v>
+      </c>
+      <c r="H15" t="s">
+        <v>56</v>
+      </c>
+      <c r="I15" t="s">
         <v>72</v>
       </c>
-      <c r="M14" t="s">
-        <v>83</v>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" t="s">
+        <v>74</v>
+      </c>
+      <c r="L15" t="s">
+        <v>75</v>
+      </c>
+      <c r="M15" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/BARQUISIMETO.xlsx
+++ b/cuadros/MAYO/BARQUISIMETO.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="97">
   <si>
     <t>SUCURSAL</t>
   </si>
@@ -100,6 +100,12 @@
     <t>PEPSI-COLA DE VENEZUELA, C.A.</t>
   </si>
   <si>
+    <t>MONDELEZ VZ, C.A.</t>
+  </si>
+  <si>
+    <t>INDUSTRIA LACTEA VENEZOLANA ,C.A.</t>
+  </si>
+  <si>
     <t>A3-023938</t>
   </si>
   <si>
@@ -133,6 +139,12 @@
     <t>7774367127</t>
   </si>
   <si>
+    <t>005466702</t>
+  </si>
+  <si>
+    <t>6200011783</t>
+  </si>
+  <si>
     <t>2026-05-01</t>
   </si>
   <si>
@@ -154,6 +166,9 @@
     <t>2026-05-13</t>
   </si>
   <si>
+    <t>2026-05-14</t>
+  </si>
+  <si>
     <t>RECEPCION</t>
   </si>
   <si>
@@ -235,6 +250,12 @@
     <t xml:space="preserve">SE DUPLICO EL SKU DE PEPSI DE 2 LTS </t>
   </si>
   <si>
+    <t>NRO DE FCTURA ERRADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SKU ERRADO </t>
+  </si>
+  <si>
     <t>SIN FOTO</t>
   </si>
   <si>
@@ -278,6 +299,12 @@
   </si>
   <si>
     <t>ID_20260513170211</t>
+  </si>
+  <si>
+    <t>ID_20260514111539</t>
+  </si>
+  <si>
+    <t>ID_20260514113726</t>
   </si>
 </sst>
 </file>
@@ -609,7 +636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -667,31 +694,31 @@
         <v>4734</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="H2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="I2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="L2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="M2">
         <v>20260504092500</v>
@@ -708,31 +735,31 @@
         <v>31976</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G3" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="H3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="L3" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="M3">
         <v>20260504112100</v>
@@ -746,34 +773,34 @@
         <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F4" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G4" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="H4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="L4" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="M4">
         <v>20260504125319</v>
@@ -787,37 +814,37 @@
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G5" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I5" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="L5" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="M5" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -828,37 +855,37 @@
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="H6" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="L6" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="M6" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -869,37 +896,37 @@
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F7" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G7" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H7" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I7" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="L7" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="M7" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -910,31 +937,31 @@
         <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G8" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="H8" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="I8" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="L8" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="M8" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -945,37 +972,37 @@
         <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E9" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F9" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G9" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="H9" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I9" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="L9" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="M9" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -986,37 +1013,37 @@
         <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E10" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F10" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G10" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H10" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I10" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="J10">
         <v>2.12</v>
       </c>
       <c r="K10" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="L10" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="M10" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1027,37 +1054,37 @@
         <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E11" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F11" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G11" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="H11" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="I11" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="L11" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="M11" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1068,37 +1095,37 @@
         <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F12" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G12" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="H12" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I12" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="L12" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="M12" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1109,37 +1136,37 @@
         <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E13" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F13" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G13" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H13" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="I13" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="L13" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="M13" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1150,37 +1177,37 @@
         <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D14" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E14" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F14" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G14" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H14" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="I14" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="L14" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="M14" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1191,37 +1218,119 @@
         <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D15" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E15" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F15" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H15" t="s">
+        <v>61</v>
+      </c>
+      <c r="I15" t="s">
+        <v>77</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" t="s">
+        <v>81</v>
+      </c>
+      <c r="L15" t="s">
+        <v>82</v>
+      </c>
+      <c r="M15" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" t="s">
         <v>50</v>
       </c>
-      <c r="H15" t="s">
+      <c r="E16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F16" t="s">
+        <v>54</v>
+      </c>
+      <c r="G16" t="s">
         <v>56</v>
       </c>
-      <c r="I15" t="s">
-        <v>72</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15" t="s">
-        <v>74</v>
-      </c>
-      <c r="L15" t="s">
-        <v>75</v>
-      </c>
-      <c r="M15" t="s">
-        <v>87</v>
+      <c r="H16" t="s">
+        <v>62</v>
+      </c>
+      <c r="I16" t="s">
+        <v>78</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" t="s">
+        <v>81</v>
+      </c>
+      <c r="L16" t="s">
+        <v>82</v>
+      </c>
+      <c r="M16" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17" t="s">
+        <v>54</v>
+      </c>
+      <c r="G17" t="s">
+        <v>57</v>
+      </c>
+      <c r="H17" t="s">
+        <v>63</v>
+      </c>
+      <c r="I17" t="s">
+        <v>79</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" t="s">
+        <v>81</v>
+      </c>
+      <c r="L17" t="s">
+        <v>82</v>
+      </c>
+      <c r="M17" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/BARQUISIMETO.xlsx
+++ b/cuadros/MAYO/BARQUISIMETO.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,8 +505,10 @@
           <t>ALIMENTOS MUNCHY, C.A.</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>4734</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>4734</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -566,8 +568,10 @@
           <t>RUBROS SANARE C2, C.A.</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>31976</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>31976</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1511,6 +1515,71 @@
       <c r="M17" t="inlineStr">
         <is>
           <t>ID_20260514113726</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BARQUISIMETO</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NESTLE DE VENEZUELA, S.A.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>00685722</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>REIDINSON MONTERO</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>NRO DE FACTURA ERRADO</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>ID_20260515102241</t>
         </is>
       </c>
     </row>
